--- a/data/trans_camb/P3A_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -624,47 +624,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,58</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>9,61</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>23,13</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-3,72</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-1,87</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-1,75</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,08</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,56</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>10,19</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,62; 6,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,73; 14,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,21; 28,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,58; -0,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,09; 1,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,45; 1,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,9; 2,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,51; 6,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,4; 13,13</t>
         </is>
       </c>
     </row>
@@ -730,47 +730,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-4,3%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-2,15%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-2,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-0,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,75; 21,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,81; 46,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>51,44; 90,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,53; -0,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,83; 1,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,08; 1,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,49; 4,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,82; 10,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,39; 21,34</t>
         </is>
       </c>
     </row>
@@ -840,47 +840,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>12,61</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>21,2</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>26,65</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>5,56</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>10,6</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>6,73</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>13,84</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>19,26</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,24; 15,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,76; 24,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,26; 35,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,12; 3,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,43; 8,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,15; 13,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,49; 9,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,58; 16,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,56; 24,78</t>
         </is>
       </c>
     </row>
@@ -946,47 +946,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,72%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26,48; 50,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>50,18; 78,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,55; 110,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,31; 4,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,04; 9,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,61; 16,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,61; 16,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,81; 28,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,57; 43,75</t>
         </is>
       </c>
     </row>
@@ -1056,47 +1056,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>12,52</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>24,14</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>30,94</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,01</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>6,94</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>11,14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>8,33</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>16,95</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>22,53</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,16; 19,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,79; 30,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,89; 36,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,27; 7,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,67; 11,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,74; 15,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,81; 12,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,61; 20,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,43; 26,57</t>
         </is>
       </c>
     </row>
@@ -1162,47 +1162,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,05%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,71; 49,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>39,7; 78,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>54,79; 95,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,99; 9,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,25; 15,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,25; 19,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,22; 22,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,28; 36,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>29,5; 46,78</t>
         </is>
       </c>
     </row>
@@ -1272,47 +1272,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>9,47</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>19,0</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>27,04</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,44</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,27</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>7,39</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>4,53</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>11,16</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>17,27</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,11; 12,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,4; 21,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,0; 32,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,32; 1,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,63; 4,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,69; 9,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,9; 6,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,56; 12,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,21; 20,55</t>
         </is>
       </c>
     </row>
@@ -1378,47 +1378,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-0,53%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,02; 36,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>46,44; 64,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36,16; 96,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,73; 1,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,93; 5,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,7; 10,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,78; 10,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,89; 21,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,95; 34,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23,13</t>
+          <t>23,41</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,75</t>
+          <t>-1,65</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,19</t>
+          <t>10,14</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 6,82</t>
+          <t>-1,9; 6,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,73; 14,14</t>
+          <t>4,69; 14,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,21; 28,32</t>
+          <t>18,37; 28,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,58; -0,87</t>
+          <t>-6,53; -0,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 1,34</t>
+          <t>-4,99; 1,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 1,04</t>
+          <t>-4,46; 1,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 2,75</t>
+          <t>-2,86; 2,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 6,66</t>
+          <t>0,56; 6,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,4; 13,13</t>
+          <t>7,15; 13,0</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-2,02%</t>
+          <t>-1,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 21,41</t>
+          <t>-5,48; 21,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,81; 46,12</t>
+          <t>13,76; 46,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51,44; 90,59</t>
+          <t>52,98; 93,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,53; -0,99</t>
+          <t>-7,46; -0,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 1,56</t>
+          <t>-5,65; 1,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 1,21</t>
+          <t>-5,08; 1,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 4,47</t>
+          <t>-4,46; 4,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 10,85</t>
+          <t>0,87; 10,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,39; 21,34</t>
+          <t>11,11; 21,32</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26,65</t>
+          <t>33,05</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,6</t>
+          <t>9,6</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19,26</t>
+          <t>21,97</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,24; 15,63</t>
+          <t>9,44; 15,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,76; 24,3</t>
+          <t>17,85; 24,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,26; 35,01</t>
+          <t>29,57; 36,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,87</t>
+          <t>-1,13; 3,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,43; 8,0</t>
+          <t>3,33; 7,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,15; 13,31</t>
+          <t>7,35; 11,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 9,08</t>
+          <t>4,42; 9,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,58; 16,06</t>
+          <t>11,44; 16,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 24,78</t>
+          <t>19,47; 24,14</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>101,66%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,48; 50,64</t>
+          <t>27,5; 51,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,18; 78,44</t>
+          <t>52,99; 80,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,55; 110,37</t>
+          <t>86,59; 118,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 4,71</t>
+          <t>-1,3; 4,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 9,76</t>
+          <t>3,92; 9,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,61; 16,18</t>
+          <t>8,68; 14,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,61; 16,18</t>
+          <t>7,57; 16,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,81; 28,77</t>
+          <t>19,58; 28,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,57; 43,75</t>
+          <t>33,2; 43,51</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30,94</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,14</t>
+          <t>10,86</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22,53</t>
+          <t>22,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,16; 19,26</t>
+          <t>5,53; 18,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,79; 30,0</t>
+          <t>18,19; 30,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,89; 36,43</t>
+          <t>24,53; 36,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 7,24</t>
+          <t>-3,2; 7,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,67; 11,87</t>
+          <t>2,12; 12,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,74; 15,01</t>
+          <t>6,63; 15,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 12,81</t>
+          <t>4,08; 13,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,61; 20,74</t>
+          <t>12,89; 21,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,43; 26,57</t>
+          <t>18,7; 25,93</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,54%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,71; 49,12</t>
+          <t>12,66; 47,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39,7; 78,33</t>
+          <t>39,74; 79,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54,79; 95,16</t>
+          <t>53,68; 93,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 9,51</t>
+          <t>-3,89; 9,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,25; 15,55</t>
+          <t>2,62; 16,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,25; 19,81</t>
+          <t>7,99; 20,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,22; 22,88</t>
+          <t>6,61; 22,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,28; 36,68</t>
+          <t>21,18; 37,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29,5; 46,78</t>
+          <t>30,3; 45,92</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27,04</t>
+          <t>31,21</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,39</t>
+          <t>6,59</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>17,27</t>
+          <t>18,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,11; 12,18</t>
+          <t>7,01; 11,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,4; 21,34</t>
+          <t>16,4; 21,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,0; 32,47</t>
+          <t>28,91; 33,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,34</t>
+          <t>-2,32; 1,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,96</t>
+          <t>1,5; 4,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,69; 9,1</t>
+          <t>5,16; 8,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,21</t>
+          <t>2,89; 6,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,56; 12,8</t>
+          <t>9,39; 12,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,21; 20,55</t>
+          <t>17,36; 20,46</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>31,74%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,02; 36,92</t>
+          <t>20,05; 36,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>46,44; 64,72</t>
+          <t>45,99; 64,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36,16; 96,72</t>
+          <t>81,34; 102,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 1,6</t>
+          <t>-2,71; 1,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,96</t>
+          <t>1,76; 5,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,7; 10,95</t>
+          <t>6,05; 9,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,78; 10,58</t>
+          <t>4,8; 10,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,89; 21,88</t>
+          <t>15,53; 21,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,95; 34,69</t>
+          <t>28,69; 35,01</t>
         </is>
       </c>
     </row>
